--- a/exports/trend_1d/SBILIFE_full_report.xlsx
+++ b/exports/trend_1d/SBILIFE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>6.1</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43046</v>
+        <v>43047</v>
       </c>
       <c r="H2" t="n">
-        <v>642.35</v>
+        <v>631.6</v>
       </c>
       <c r="I2" t="n">
         <v>631.99</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.56</v>
+        <v>-6.16</v>
       </c>
       <c r="L2" t="n">
-        <v>4.98</v>
+        <v>6.54</v>
       </c>
       <c r="M2" t="n">
         <v>0.55</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.31</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43059</v>
+        <v>43060</v>
       </c>
       <c r="H3" t="n">
-        <v>661.45</v>
+        <v>687.45</v>
       </c>
       <c r="I3" t="n">
         <v>684.0954431570675</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.73</v>
+        <v>-8.84</v>
       </c>
       <c r="L3" t="n">
-        <v>7.79</v>
+        <v>10.26</v>
       </c>
       <c r="M3" t="n">
         <v>1.04</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.44</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H4" t="n">
-        <v>681.85</v>
+        <v>667.9</v>
       </c>
       <c r="I4" t="n">
         <v>671.8598954145737</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.84</v>
       </c>
       <c r="L4" t="n">
         <v>5.33</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43200</v>
+        <v>43201</v>
       </c>
       <c r="H5" t="n">
-        <v>695.7</v>
+        <v>719</v>
       </c>
       <c r="I5" t="n">
         <v>708.5250018630394</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.16</v>
+        <v>-7.65</v>
       </c>
       <c r="L5" t="n">
         <v>9.779999999999999</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43223</v>
+        <v>43224</v>
       </c>
       <c r="H6" t="n">
-        <v>732</v>
+        <v>702.1</v>
       </c>
       <c r="I6" t="n">
         <v>703.7242366326426</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>1.81</v>
+        <v>-2.35</v>
       </c>
       <c r="L6" t="n">
         <v>3.89</v>
@@ -783,7 +854,7 @@
         <v>1.68</v>
       </c>
       <c r="N6" t="n">
-        <v>2.08</v>
+        <v>4.08</v>
       </c>
       <c r="O6" t="n">
         <v>3.35</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>11.81</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43307</v>
+        <v>43308</v>
       </c>
       <c r="H7" t="n">
-        <v>673.2</v>
+        <v>694.05</v>
       </c>
       <c r="I7" t="n">
         <v>674.2943780317154</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>4.12</v>
+        <v>1.15</v>
       </c>
       <c r="L7" t="n">
         <v>3.96</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>1.72</v>
       </c>
       <c r="N7" t="n">
         <v>3.11</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43357</v>
+        <v>43360</v>
       </c>
       <c r="H8" t="n">
-        <v>670.05</v>
+        <v>642.65</v>
       </c>
       <c r="I8" t="n">
         <v>643.8992135444471</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.46</v>
+        <v>-7.41</v>
       </c>
       <c r="L8" t="n">
-        <v>7.21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M8" t="n">
         <v>0.89</v>
       </c>
       <c r="N8" t="n">
-        <v>3.49</v>
+        <v>4.09</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43454</v>
+        <v>43455</v>
       </c>
       <c r="H9" t="n">
-        <v>592.45</v>
+        <v>597.5</v>
       </c>
       <c r="I9" t="n">
         <v>595.200993320326</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K9" t="n">
-        <v>7.81</v>
+        <v>7.03</v>
       </c>
       <c r="L9" t="n">
         <v>4.04</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.13</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43501</v>
+        <v>43502</v>
       </c>
       <c r="H10" t="n">
-        <v>584</v>
+        <v>579.4</v>
       </c>
       <c r="I10" t="n">
         <v>579.9843020879365</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.26</v>
+        <v>-3.03</v>
       </c>
       <c r="L10" t="n">
         <v>9.56</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>10.1</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H11" t="n">
-        <v>578.55</v>
+        <v>607.9</v>
       </c>
       <c r="I11" t="n">
         <v>599.2495335986151</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>0.15</v>
+        <v>-4.92</v>
       </c>
       <c r="L11" t="n">
-        <v>1.83</v>
+        <v>7.37</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.71</v>
+        <v>5.07</v>
       </c>
       <c r="O11" t="n">
         <v>-0.79</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>17.55</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43598</v>
+        <v>43599</v>
       </c>
       <c r="H12" t="n">
-        <v>620</v>
+        <v>615.6</v>
       </c>
       <c r="I12" t="n">
         <v>616.8364430314758</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K12" t="n">
-        <v>1.99</v>
+        <v>1.27</v>
       </c>
       <c r="L12" t="n">
         <v>15.19</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>10.36</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43608</v>
+        <v>43609</v>
       </c>
       <c r="H13" t="n">
-        <v>671.4</v>
+        <v>686</v>
       </c>
       <c r="I13" t="n">
         <v>679.4014295043438</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.06</v>
+        <v>-11.44</v>
       </c>
       <c r="L13" t="n">
-        <v>11.09</v>
+        <v>12.09</v>
       </c>
       <c r="M13" t="n">
         <v>2.24</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.93</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H14" t="n">
-        <v>994.1</v>
+        <v>893.1</v>
       </c>
       <c r="I14" t="n">
         <v>942.5538886155261</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K14" t="n">
-        <v>44.91</v>
+        <v>30.19</v>
       </c>
       <c r="L14" t="n">
         <v>3.04</v>
@@ -1239,7 +1406,7 @@
         <v>5.01</v>
       </c>
       <c r="N14" t="n">
-        <v>6.35</v>
+        <v>10.16</v>
       </c>
       <c r="O14" t="n">
         <v>2.17</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>17.78</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H15" t="n">
-        <v>779.5</v>
+        <v>807.1</v>
       </c>
       <c r="I15" t="n">
         <v>785.0464247012862</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K15" t="n">
-        <v>12.72</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L15" t="n">
         <v>13.41</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.95</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H16" t="n">
-        <v>851.55</v>
+        <v>827.75</v>
       </c>
       <c r="I16" t="n">
         <v>837.1841482728512</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K16" t="n">
-        <v>5.51</v>
+        <v>2.56</v>
       </c>
       <c r="L16" t="n">
         <v>9.710000000000001</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>10.11</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44144</v>
+        <v>44145</v>
       </c>
       <c r="H17" t="n">
-        <v>808.15</v>
+        <v>829.4</v>
       </c>
       <c r="I17" t="n">
         <v>822.3590187526622</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K17" t="n">
-        <v>2.37</v>
+        <v>-0.2</v>
       </c>
       <c r="L17" t="n">
         <v>5.83</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.78</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H18" t="n">
-        <v>878.3</v>
+        <v>862.55</v>
       </c>
       <c r="I18" t="n">
         <v>877.5555560642611</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K18" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>2.18</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44263</v>
+        <v>44264</v>
       </c>
       <c r="H19" t="n">
-        <v>923.85</v>
+        <v>971.3</v>
       </c>
       <c r="I19" t="n">
         <v>934.1551513622439</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K19" t="n">
-        <v>-7.11</v>
+        <v>-12.61</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9</v>
+        <v>14.05</v>
       </c>
       <c r="M19" t="n">
-        <v>1.54</v>
+        <v>2.83</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>5.14</v>
       </c>
       <c r="O19" t="n">
         <v>-1.79</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.66</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H20" t="n">
-        <v>880.7</v>
+        <v>864.1</v>
       </c>
       <c r="I20" t="n">
         <v>877.4322530194523</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" t="n">
-        <v>-9.33</v>
+        <v>-11.04</v>
       </c>
       <c r="L20" t="n">
-        <v>9.91</v>
+        <v>11.36</v>
       </c>
       <c r="M20" t="n">
         <v>3.79</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.58</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44309</v>
+        <v>44312</v>
       </c>
       <c r="H21" t="n">
-        <v>922.85</v>
+        <v>942.5</v>
       </c>
       <c r="I21" t="n">
         <v>940.2632719765838</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.8</v>
+        <v>-9.07</v>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>9.58</v>
       </c>
       <c r="M21" t="n">
         <v>1.19</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H22" t="n">
-        <v>1168.75</v>
+        <v>1158.3</v>
       </c>
       <c r="I22" t="n">
         <v>1166.220844645575</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K22" t="n">
-        <v>24.01</v>
+        <v>22.9</v>
       </c>
       <c r="L22" t="n">
         <v>3.01</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.77</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44561</v>
+        <v>44564</v>
       </c>
       <c r="H23" t="n">
-        <v>1196</v>
+        <v>1209.4</v>
       </c>
       <c r="I23" t="n">
         <v>1205.476939395777</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.25</v>
+        <v>-4.41</v>
       </c>
       <c r="L23" t="n">
         <v>5.48</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.42</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44588</v>
+        <v>44589</v>
       </c>
       <c r="H24" t="n">
-        <v>1211.65</v>
+        <v>1205.55</v>
       </c>
       <c r="I24" t="n">
         <v>1207.586880040971</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="L24" t="n">
         <v>1.11</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.34</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44658</v>
+        <v>44659</v>
       </c>
       <c r="H25" t="n">
-        <v>1108.85</v>
+        <v>1160.45</v>
       </c>
       <c r="I25" t="n">
         <v>1136.431920473943</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K25" t="n">
-        <v>8.02</v>
+        <v>3.74</v>
       </c>
       <c r="L25" t="n">
         <v>3.69</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>9.84</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H26" t="n">
-        <v>1083.65</v>
+        <v>1059.15</v>
       </c>
       <c r="I26" t="n">
         <v>1064.646686796051</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.62</v>
+        <v>-8.73</v>
       </c>
       <c r="L26" t="n">
-        <v>8.550000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="M26" t="n">
         <v>1.52</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.28</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H27" t="n">
-        <v>1148.4</v>
+        <v>1174.15</v>
       </c>
       <c r="I27" t="n">
         <v>1149.775267840527</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.43</v>
+        <v>-10.86</v>
       </c>
       <c r="L27" t="n">
-        <v>8.58</v>
+        <v>11.5</v>
       </c>
       <c r="M27" t="n">
         <v>2.3</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>9.73</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44733</v>
+        <v>44734</v>
       </c>
       <c r="H28" t="n">
-        <v>1096.35</v>
+        <v>1070.45</v>
       </c>
       <c r="I28" t="n">
         <v>1071.181590762071</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>-6.63</v>
+        <v>-8.83</v>
       </c>
       <c r="L28" t="n">
-        <v>8.94</v>
+        <v>9.5</v>
       </c>
       <c r="M28" t="n">
         <v>1.55</v>
       </c>
       <c r="N28" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="O28" t="n">
         <v>2.24</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>8.94</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44756</v>
+        <v>44757</v>
       </c>
       <c r="H29" t="n">
-        <v>1138.95</v>
+        <v>1155.45</v>
       </c>
       <c r="I29" t="n">
         <v>1151.49184433908</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.4</v>
+        <v>-7.94</v>
       </c>
       <c r="L29" t="n">
-        <v>7.91</v>
+        <v>8.19</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.32</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44844</v>
+        <v>44845</v>
       </c>
       <c r="H30" t="n">
-        <v>1239.3</v>
+        <v>1206.35</v>
       </c>
       <c r="I30" t="n">
         <v>1230.981172286655</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="n">
-        <v>7.26</v>
+        <v>4.41</v>
       </c>
       <c r="L30" t="n">
         <v>2.01</v>
@@ -2151,7 +2510,7 @@
         <v>4.39</v>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="O30" t="n">
         <v>1.45</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44867</v>
+        <v>44868</v>
       </c>
       <c r="H31" t="n">
-        <v>1272.65</v>
+        <v>1276.05</v>
       </c>
       <c r="I31" t="n">
         <v>1272.824039283132</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.5</v>
+        <v>-5.78</v>
       </c>
       <c r="L31" t="n">
         <v>6.64</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>6.19</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44953</v>
+        <v>44956</v>
       </c>
       <c r="H32" t="n">
-        <v>1250.25</v>
+        <v>1233.45</v>
       </c>
       <c r="I32" t="n">
         <v>1239.615497640794</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.02</v>
+        <v>-3.34</v>
       </c>
       <c r="L32" t="n">
         <v>5.57</v>
       </c>
       <c r="M32" t="n">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="N32" t="n">
         <v>2.86</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.44</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45049</v>
+        <v>45050</v>
       </c>
       <c r="H33" t="n">
-        <v>1136.9</v>
+        <v>1167.45</v>
       </c>
       <c r="I33" t="n">
         <v>1152.62208110021</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K33" t="n">
-        <v>7.83</v>
+        <v>5.35</v>
       </c>
       <c r="L33" t="n">
         <v>0.89</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.02</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45191</v>
+        <v>45194</v>
       </c>
       <c r="H34" t="n">
-        <v>1318.85</v>
+        <v>1294.15</v>
       </c>
       <c r="I34" t="n">
         <v>1309.192505073549</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K34" t="n">
-        <v>12.97</v>
+        <v>10.85</v>
       </c>
       <c r="L34" t="n">
         <v>2.61</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.87</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45216</v>
+        <v>45217</v>
       </c>
       <c r="H35" t="n">
-        <v>1348.35</v>
+        <v>1356.35</v>
       </c>
       <c r="I35" t="n">
         <v>1349.289966924523</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.19</v>
+        <v>-4.81</v>
       </c>
       <c r="L35" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="M35" t="n">
         <v>0.61</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.65</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45281</v>
+        <v>45282</v>
       </c>
       <c r="H36" t="n">
-        <v>1403.75</v>
+        <v>1394.3</v>
       </c>
       <c r="I36" t="n">
         <v>1395.206501935248</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K36" t="n">
-        <v>3.49</v>
+        <v>2.8</v>
       </c>
       <c r="L36" t="n">
         <v>4.84</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.59</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="H37" t="n">
-        <v>1453.35</v>
+        <v>1508.45</v>
       </c>
       <c r="I37" t="n">
         <v>1480.218554670542</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.24</v>
+        <v>-8.19</v>
       </c>
       <c r="L37" t="n">
-        <v>7.25</v>
+        <v>8.74</v>
       </c>
       <c r="M37" t="n">
         <v>0.85</v>
       </c>
       <c r="N37" t="n">
-        <v>3.11</v>
+        <v>3.79</v>
       </c>
       <c r="O37" t="n">
         <v>-0.67</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45406</v>
+        <v>45407</v>
       </c>
       <c r="H38" t="n">
-        <v>1460.05</v>
+        <v>1444.45</v>
       </c>
       <c r="I38" t="n">
         <v>1445.457753588361</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.21</v>
+        <v>-4.24</v>
       </c>
       <c r="L38" t="n">
         <v>5.51</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>6.72</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45470</v>
+        <v>45471</v>
       </c>
       <c r="H39" t="n">
-        <v>1463.45</v>
+        <v>1491.95</v>
       </c>
       <c r="I39" t="n">
         <v>1473.940331246373</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.32</v>
+        <v>-3.29</v>
       </c>
       <c r="L39" t="n">
-        <v>2.52</v>
+        <v>3.76</v>
       </c>
       <c r="M39" t="n">
         <v>3.53</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>8.35</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H40" t="n">
-        <v>1805.55</v>
+        <v>1798.1</v>
       </c>
       <c r="I40" t="n">
         <v>1800.584617587676</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K40" t="n">
-        <v>21.02</v>
+        <v>20.52</v>
       </c>
       <c r="L40" t="n">
         <v>2.81</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="H41" t="n">
-        <v>1434.65</v>
+        <v>1477.75</v>
       </c>
       <c r="I41" t="n">
         <v>1476.876303134578</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K41" t="n">
-        <v>20.21</v>
+        <v>17.82</v>
       </c>
       <c r="L41" t="n">
         <v>2.89</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.43</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45716</v>
+        <v>45719</v>
       </c>
       <c r="H42" t="n">
-        <v>1430.5</v>
+        <v>1408.5</v>
       </c>
       <c r="I42" t="n">
         <v>1413.774580679104</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.2</v>
+        <v>-4.69</v>
       </c>
       <c r="L42" t="n">
         <v>7.12</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.93</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45735</v>
+        <v>45736</v>
       </c>
       <c r="H43" t="n">
-        <v>1484.9</v>
+        <v>1498.35</v>
       </c>
       <c r="I43" t="n">
         <v>1494.34974017229</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.42</v>
+        <v>-6.38</v>
       </c>
       <c r="L43" t="n">
-        <v>5.71</v>
+        <v>6.94</v>
       </c>
       <c r="M43" t="n">
         <v>1.29</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.57</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H44" t="n">
-        <v>1785.1</v>
+        <v>1770.9</v>
       </c>
       <c r="I44" t="n">
         <v>1778.701165196494</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K44" t="n">
-        <v>19.14</v>
+        <v>18.19</v>
       </c>
       <c r="L44" t="n">
         <v>4.52</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>5.32</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="H45" t="n">
-        <v>1839.8</v>
+        <v>1903.1</v>
       </c>
       <c r="I45" t="n">
         <v>1865.13219632267</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.89</v>
+        <v>-7.47</v>
       </c>
       <c r="L45" t="n">
-        <v>5.27</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>0.84</v>
+        <v>2.2</v>
       </c>
       <c r="N45" t="n">
-        <v>2.08</v>
+        <v>3.44</v>
       </c>
       <c r="O45" t="n">
         <v>-0.8</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.7</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H46" t="n">
-        <v>1998.5</v>
+        <v>1974.3</v>
       </c>
       <c r="I46" t="n">
         <v>1993.724873736604</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K46" t="n">
-        <v>5.01</v>
+        <v>3.74</v>
       </c>
       <c r="L46" t="n">
         <v>1.2</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.68</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H47" t="n">
-        <v>1904</v>
+        <v>1923.2</v>
       </c>
       <c r="I47" t="n">
         <v>1913.373067378234</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K47" t="n">
-        <v>3.56</v>
+        <v>2.59</v>
       </c>
       <c r="L47" t="n">
         <v>7.99</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="H48" t="n">
-        <v>1884.8</v>
+        <v>1828.1</v>
       </c>
       <c r="I48" t="n">
         <v>1830.222789122455</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K48" t="n">
-        <v>-2</v>
+        <v>-4.94</v>
       </c>
       <c r="L48" t="n">
-        <v>2.25</v>
+        <v>6.01</v>
       </c>
       <c r="M48" t="n">
-        <v>0.74</v>
+        <v>1.05</v>
       </c>
       <c r="N48" t="n">
         <v>3.58</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.99</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="H49" t="n">
-        <v>1821.7</v>
+        <v>1862.9</v>
       </c>
       <c r="I49" t="n">
         <v>1833.09617019297</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K49" t="n">
-        <v>0.35</v>
+        <v>-1.9</v>
       </c>
       <c r="L49" t="n">
         <v>4.31</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.53</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="H50" t="n">
-        <v>1790.4</v>
+        <v>1778</v>
       </c>
       <c r="I50" t="n">
         <v>1785.312535635507</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.89</v>
+        <v>-4.56</v>
       </c>
       <c r="L50" t="n">
-        <v>4.4</v>
+        <v>5.39</v>
       </c>
       <c r="M50" t="n">
         <v>0.82</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3351,6 +3962,14 @@
       <c r="Q51" t="n">
         <v>49</v>
       </c>
+      <c r="R51" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7187,7 +7806,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.5</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -7197,7 +7816,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -7207,7 +7826,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
@@ -7217,7 +7836,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -7227,7 +7846,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -7237,7 +7856,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -7247,7 +7866,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -7257,7 +7876,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -7267,7 +7886,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.7</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="14">
@@ -7277,7 +7896,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="15">
@@ -7287,7 +7906,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.21</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="16">
@@ -7297,7 +7916,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.31</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="17">
@@ -7307,7 +7926,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.91</v>
+        <v>30.19</v>
       </c>
     </row>
     <row r="18">
@@ -7317,7 +7936,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.9</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="19">
@@ -7327,7 +7946,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.79</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="20">
@@ -7337,7 +7956,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.33</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="21">
@@ -7357,7 +7976,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -7367,7 +7986,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -7377,7 +7996,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="25">
@@ -7397,7 +8016,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.43</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="27">
@@ -7417,7 +8036,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
